--- a/trunk/recursos/formatos_layout/formato_layout_num_oficios/FORMATO_LAYOUT_OFICIOS.xlsx
+++ b/trunk/recursos/formatos_layout/formato_layout_num_oficios/FORMATO_LAYOUT_OFICIOS.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>FECHA OFICIO</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>CODIGO_PRIORIDAD</t>
+  </si>
+  <si>
+    <t>ID INSUMO</t>
   </si>
 </sst>
 </file>
@@ -148,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -163,6 +166,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,47 +519,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35" style="2" customWidth="1"/>
-    <col min="5" max="5" width="48" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" style="10" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35" style="2" customWidth="1"/>
+    <col min="6" max="6" width="48" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="6" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" s="6" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
